--- a/exports/export-yazd.xlsx
+++ b/exports/export-yazd.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="202">
   <si>
     <t>فهرست اسامی شرکت های دولتی و خصوصی شاخص</t>
   </si>
@@ -454,7 +454,7 @@
     <t>وضعیت اجرا</t>
   </si>
   <si>
-    <t>در حال اجرا</t>
+    <t>متوقف‌شده (قابل ادامه)</t>
   </si>
   <si>
     <t>زمان شروع</t>
@@ -472,117 +472,123 @@
     <t>منابع بررسی‌شده</t>
   </si>
   <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>شرکت‌های شناسایی‌شده (نامزدها)</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>درخواست‌های انجام‌شده</t>
+  </si>
+  <si>
+    <t>127 از 200</t>
+  </si>
+  <si>
+    <t>رکوردهای جدید</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>به‌روزرسانی‌شده</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>شرکت‌های شناسایی‌شده (نامزدها)</t>
-  </si>
-  <si>
-    <t>درخواست‌های انجام‌شده</t>
-  </si>
-  <si>
-    <t>0 از 200</t>
-  </si>
-  <si>
-    <t>رکوردهای جدید</t>
-  </si>
-  <si>
-    <t>به‌روزرسانی‌شده</t>
-  </si>
-  <si>
     <t>موارد نامطمئن</t>
   </si>
   <si>
     <t>خطاها</t>
   </si>
   <si>
+    <t>1 مورد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ↳ خطا</t>
+  </si>
+  <si>
+    <t>سرویس هوش مصنوعی پیاپی محدودشده است (429) — کار برای جلوگیری از هدررفت بودجه موقتاً متوقف شد؛ کمی بعد «ادامه» را بزنید.</t>
+  </si>
+  <si>
+    <t>محدودیت‌های پوشش</t>
+  </si>
+  <si>
+    <t>پوشش کامل تضمین نمی‌شود؛ فهرست منابع بررسی‌شده ملاک است.</t>
+  </si>
+  <si>
+    <t>کار: استخراج استان کرمانشاه — ۲۰۰ درخواست</t>
+  </si>
+  <si>
+    <t>استان‌ها: کرمانشاه | شهرها: کرمانشاه، اسلام‌آباد غرب، سنقر، هرسین، کنگاور، جوانرود، صحنه، قصر شیرین</t>
+  </si>
+  <si>
+    <t>2026-10-28 17:02</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>200 از 200</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4 مورد</t>
+  </si>
+  <si>
+    <t>کشف هوشمند در دسترس نیست: سرویس هوش مصنوعی پاسخ نداد: API request failed with status 429: {"error":"Too many requests, please try again later"}</t>
+  </si>
+  <si>
+    <t>سرویس هوش مصنوعی موقتاً پاسخ نداد (سرویس هوش مصنوعی پاسخ نداد: API request failed with status 429: {"error":"Too many requests, please try again later"}) — کار برای ادامه بعدی متوقف شد؛ چند لحظه دیگر «ادامه» را بزنید.</t>
+  </si>
+  <si>
+    <t>سقف بودجه درخواست‌ها پر شد؛ کار موقتاً متوقف شد (قابل ادامه)</t>
+  </si>
+  <si>
+    <t>کار: استخراج استان همدان — ۲۰۰ درخواست</t>
+  </si>
+  <si>
+    <t>استان‌ها: همدان | شهرها: همدان، ملایر، نهاوند، تویسرکان، اسدآباد، بهار، کبودرآهنگ، رزن</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>کار: آزمون کرمانشاه</t>
+  </si>
+  <si>
+    <t>استان‌ها: کرمانشاه | شهرها: —</t>
+  </si>
+  <si>
+    <t>2026-10-28 14:39</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>3 از 5</t>
+  </si>
+  <si>
     <t>0 مورد</t>
   </si>
   <si>
-    <t>محدودیت‌های پوشش</t>
-  </si>
-  <si>
-    <t>پوشش کامل تضمین نمی‌شود؛ فهرست منابع بررسی‌شده ملاک است.</t>
-  </si>
-  <si>
-    <t>کار: استخراج استان کرمانشاه — ۲۰۰ درخواست</t>
-  </si>
-  <si>
-    <t>استان‌ها: کرمانشاه | شهرها: کرمانشاه، اسلام‌آباد غرب، سنقر، هرسین، کنگاور، جوانرود، صحنه، قصر شیرین</t>
-  </si>
-  <si>
-    <t>2026-10-28 17:02</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>179 از 200</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3 مورد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ↳ خطا</t>
-  </si>
-  <si>
-    <t>کشف هوشمند در دسترس نیست: سرویس هوش مصنوعی پاسخ نداد: API request failed with status 429: {"error":"Too many requests, please try again later"}</t>
-  </si>
-  <si>
-    <t>سرویس هوش مصنوعی پیاپی محدودشده است (429) — کار برای جلوگیری از هدررفت بودجه موقتاً متوقف شد؛ کمی بعد «ادامه» را بزنید.</t>
-  </si>
-  <si>
-    <t>سرویس هوش مصنوعی موقتاً پاسخ نداد (سرویس هوش مصنوعی پاسخ نداد: API request failed with status 429: {"error":"Too many requests, please try again later"}) — کار برای ادامه بعدی متوقف شد؛ چند لحظه دیگر «ادامه» را بزنید.</t>
-  </si>
-  <si>
-    <t>کار: استخراج استان همدان — ۲۰۰ درخواست</t>
-  </si>
-  <si>
-    <t>استان‌ها: همدان | شهرها: همدان، ملایر، نهاوند، تویسرکان، اسدآباد، بهار، کبودرآهنگ، رزن</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>164 از 200</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>کار: آزمون کرمانشاه</t>
-  </si>
-  <si>
-    <t>استان‌ها: کرمانشاه | شهرها: —</t>
-  </si>
-  <si>
-    <t>متوقف‌شده (قابل ادامه)</t>
-  </si>
-  <si>
-    <t>2026-10-28 14:39</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>3 از 5</t>
-  </si>
-  <si>
     <t>کار: تست دود</t>
   </si>
   <si>
@@ -604,13 +610,10 @@
     <t>2 مورد</t>
   </si>
   <si>
-    <t>سقف بودجه درخواست‌ها پر شد؛ کار موقتاً متوقف شد (قابل ادامه)</t>
-  </si>
-  <si>
     <t>تعداد کل شرکت‌های پایگاه داده</t>
   </si>
   <si>
-    <t>80</t>
+    <t>118</t>
   </si>
   <si>
     <t>تعداد تأیید انسانی</t>
@@ -3354,7 +3357,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3419,127 +3422,127 @@
         <v>153</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>19</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>164</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3547,143 +3550,143 @@
         <v>157</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>162</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>146</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3691,20 +3694,20 @@
         <v>159</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>175</v>
@@ -3712,111 +3715,111 @@
     </row>
     <row r="48" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>162</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>19</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>185</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="58" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
     </row>
     <row r="62" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>160</v>
@@ -3824,146 +3827,170 @@
     </row>
     <row r="63" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B63" s="7" t="s">
-        <v>162</v>
+      <c r="B64" s="7" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
     </row>
     <row r="66" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>162</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="81" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="8" t="s">
-        <v>197</v>
+      <c r="A81" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="B81" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="8" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="8" t="s">
+      <c r="B84" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B82" s="7" t="s">
+    </row>
+    <row r="85" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="8" t="s">
         <v>200</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
